--- a/data/coins.xlsx
+++ b/data/coins.xlsx
@@ -23,55 +23,55 @@
     <t>Клиент</t>
   </si>
   <si>
+    <t>a4bc418f-2729-4431-bed3-7c123d84a2fe</t>
+  </si>
+  <si>
+    <t>Alexan</t>
+  </si>
+  <si>
+    <t>28b8882a-8843-4d87-8ed9-c2f47c82cde7</t>
+  </si>
+  <si>
+    <t>Гогер</t>
+  </si>
+  <si>
+    <t>d2209f0c-56c0-4bbc-a6f7-ed4bf639eec5</t>
+  </si>
+  <si>
+    <t>Городен</t>
+  </si>
+  <si>
+    <t>c71269f7-e745-45ec-8fc9-186b8271d70a</t>
+  </si>
+  <si>
+    <t>Лейбов</t>
+  </si>
+  <si>
+    <t>c12aca37-9c5e-4167-bd84-a68f382d657a</t>
+  </si>
+  <si>
+    <t>Шувалов</t>
+  </si>
+  <si>
     <t>СТАТУС</t>
   </si>
   <si>
     <t>ГП2</t>
   </si>
   <si>
-    <t>a4bc418f-2729-4431-bed3-7c123d84a2fe</t>
-  </si>
-  <si>
     <t>Княжество</t>
   </si>
   <si>
-    <t>Alexan</t>
-  </si>
-  <si>
     <t>Князь</t>
   </si>
   <si>
     <t>номинал</t>
   </si>
   <si>
-    <t>28b8882a-8843-4d87-8ed9-c2f47c82cde7</t>
-  </si>
-  <si>
-    <t>Гогер</t>
-  </si>
-  <si>
-    <t>d2209f0c-56c0-4bbc-a6f7-ed4bf639eec5</t>
-  </si>
-  <si>
-    <t>Городен</t>
-  </si>
-  <si>
     <t>описание</t>
   </si>
   <si>
-    <t>c71269f7-e745-45ec-8fc9-186b8271d70a</t>
-  </si>
-  <si>
-    <t>Лейбов</t>
-  </si>
-  <si>
     <t>R</t>
-  </si>
-  <si>
-    <t>c12aca37-9c5e-4167-bd84-a68f382d657a</t>
-  </si>
-  <si>
-    <t>Шувалов</t>
   </si>
   <si>
     <t>вход</t>
@@ -567,11 +567,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <color theme="1"/>
       <name val="&quot;Arial Cyr&quot;"/>
     </font>
     <font>
+      <b/>
       <color theme="1"/>
       <name val="&quot;Arial Cyr&quot;"/>
     </font>
@@ -634,16 +634,16 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
@@ -652,35 +652,35 @@
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="9" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="9" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -928,25 +928,25 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>8</v>
+        <v>14</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I1" s="7" t="s">
         <v>20</v>
@@ -960,7 +960,7 @@
       <c r="L1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="5" t="s">
         <v>24</v>
       </c>
       <c r="N1" s="1" t="s">
@@ -986,25 +986,25 @@
       <c r="C2" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H2" s="10">
         <v>5.0</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="4">
         <v>10000.0</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="4" t="s">
         <v>35</v>
       </c>
       <c r="K2" s="11"/>
@@ -1015,12 +1015,12 @@
         <v>14000.0</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="P2" s="5">
+        <v>3</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="P2" s="4">
         <v>4000.0</v>
       </c>
       <c r="Q2" s="14">
@@ -1037,41 +1037,41 @@
       <c r="C3" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H3" s="10">
         <v>1.0</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="4">
         <v>15000.0</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="4" t="s">
         <v>39</v>
       </c>
       <c r="K3" s="11"/>
       <c r="L3" s="15">
         <v>46001.0</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M3" s="4">
         <v>120000.0</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="P3" s="5">
+        <v>3</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="P3" s="4">
         <v>105000.0</v>
       </c>
       <c r="Q3" s="14">
@@ -1088,41 +1088,41 @@
       <c r="C4" s="9">
         <v>1111.0</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>43</v>
       </c>
       <c r="H4" s="10">
         <v>4.0</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="4">
         <v>30000.0</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="4" t="s">
         <v>44</v>
       </c>
       <c r="K4" s="11"/>
       <c r="L4" s="12">
         <v>46010.0</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M4" s="4">
         <v>40000.0</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="P4" s="5">
+        <v>3</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="P4" s="4">
         <v>10000.0</v>
       </c>
       <c r="Q4" s="14">
@@ -1139,41 +1139,41 @@
       <c r="C5" s="10">
         <v>4745.0</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="4" t="s">
         <v>48</v>
       </c>
       <c r="H5" s="10">
         <v>3.0</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="4">
         <v>45000.0</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="4" t="s">
         <v>44</v>
       </c>
       <c r="K5" s="11"/>
       <c r="L5" s="15">
         <v>46019.0</v>
       </c>
-      <c r="M5" s="5">
+      <c r="M5" s="4">
         <v>95000.0</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="P5" s="5">
+        <v>3</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
         <v>50000.0</v>
       </c>
       <c r="Q5" s="14">
@@ -1188,39 +1188,39 @@
         <v>29</v>
       </c>
       <c r="C6" s="16"/>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="4" t="s">
         <v>52</v>
       </c>
       <c r="H6" s="16"/>
-      <c r="I6" s="5">
+      <c r="I6" s="4">
         <v>8000.0</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="4" t="s">
         <v>44</v>
       </c>
       <c r="K6" s="11"/>
       <c r="L6" s="15">
         <v>46028.0</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M6" s="4">
         <v>14000.0</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="P6" s="5">
+        <v>3</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="P6" s="4">
         <v>6000.0</v>
       </c>
       <c r="Q6" s="14">
@@ -1235,39 +1235,39 @@
         <v>29</v>
       </c>
       <c r="C7" s="16"/>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="4" t="s">
         <v>52</v>
       </c>
       <c r="H7" s="16"/>
-      <c r="I7" s="5">
+      <c r="I7" s="4">
         <v>8000.0</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="4" t="s">
         <v>44</v>
       </c>
       <c r="K7" s="11"/>
       <c r="L7" s="15">
         <v>46037.0</v>
       </c>
-      <c r="M7" s="5">
+      <c r="M7" s="4">
         <v>15000.0</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="P7" s="5">
+        <v>3</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="P7" s="4">
         <v>7000.0</v>
       </c>
       <c r="Q7" s="14">
@@ -1284,41 +1284,41 @@
       <c r="C8" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="4" t="s">
         <v>57</v>
       </c>
       <c r="H8" s="10">
         <v>4.0</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="4">
         <v>20000.0</v>
       </c>
-      <c r="J8" s="5" t="s">
-        <v>11</v>
+      <c r="J8" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="K8" s="11"/>
       <c r="L8" s="12">
         <v>46046.0</v>
       </c>
-      <c r="M8" s="5">
+      <c r="M8" s="4">
         <v>39000.0</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="P8" s="5">
+        <v>3</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="4">
         <v>19000.0</v>
       </c>
       <c r="Q8" s="14">
@@ -1335,41 +1335,41 @@
       <c r="C9" s="10">
         <v>1580.0</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="4" t="s">
         <v>59</v>
       </c>
       <c r="H9" s="10">
         <v>2.0</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="4">
         <v>20000.0</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J9" s="4" t="s">
         <v>44</v>
       </c>
       <c r="K9" s="11"/>
       <c r="L9" s="15">
         <v>46055.0</v>
       </c>
-      <c r="M9" s="5">
+      <c r="M9" s="4">
         <v>45000.0</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="P9" s="5">
+        <v>3</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="P9" s="4">
         <v>25000.0</v>
       </c>
       <c r="Q9" s="14">
@@ -1386,41 +1386,41 @@
       <c r="C10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="4" t="s">
         <v>62</v>
       </c>
       <c r="H10" s="10">
         <v>1.0</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10" s="4">
         <v>50000.0</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="J10" s="4" t="s">
         <v>44</v>
       </c>
       <c r="K10" s="11"/>
       <c r="L10" s="12">
         <v>46064.0</v>
       </c>
-      <c r="M10" s="5">
+      <c r="M10" s="4">
         <v>120000.0</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O10" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="P10" s="5">
+        <v>3</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="P10" s="4">
         <v>70000.0</v>
       </c>
       <c r="Q10" s="14">
@@ -1435,13 +1435,13 @@
         <v>29</v>
       </c>
       <c r="C11" s="16"/>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G11" s="17" t="s">
@@ -1450,26 +1450,26 @@
       <c r="H11" s="10">
         <v>2.0</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="4">
         <v>15000.0</v>
       </c>
-      <c r="J11" s="5" t="s">
-        <v>11</v>
+      <c r="J11" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="K11" s="11"/>
       <c r="L11" s="15">
         <v>46073.0</v>
       </c>
-      <c r="M11" s="5">
+      <c r="M11" s="4">
         <v>45000.0</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O11" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="P11" s="5">
+        <v>3</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="P11" s="4">
         <v>30000.0</v>
       </c>
       <c r="Q11" s="14">
@@ -1486,41 +1486,41 @@
       <c r="C12" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>67</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="4" t="s">
         <v>69</v>
       </c>
       <c r="H12" s="10">
         <v>4.0</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="4">
         <v>6000.0</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="J12" s="4" t="s">
         <v>70</v>
       </c>
       <c r="K12" s="11"/>
       <c r="L12" s="12">
         <v>46082.0</v>
       </c>
-      <c r="M12" s="5">
+      <c r="M12" s="4">
         <v>22000.0</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O12" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="P12" s="5">
+        <v>3</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="P12" s="4">
         <v>16000.0</v>
       </c>
       <c r="Q12" s="14">
@@ -1537,41 +1537,41 @@
       <c r="C13" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>67</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="4" t="s">
         <v>73</v>
       </c>
       <c r="H13" s="10">
         <v>2.0</v>
       </c>
-      <c r="I13" s="5">
+      <c r="I13" s="4">
         <v>36000.0</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="J13" s="4" t="s">
         <v>70</v>
       </c>
       <c r="K13" s="11"/>
       <c r="L13" s="15">
         <v>46091.0</v>
       </c>
-      <c r="M13" s="5">
+      <c r="M13" s="4">
         <v>41000.0</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O13" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="P13" s="5">
+        <v>3</v>
+      </c>
+      <c r="O13" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="P13" s="4">
         <v>5000.0</v>
       </c>
       <c r="Q13" s="14">
@@ -1588,41 +1588,41 @@
       <c r="C14" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="4" t="s">
         <v>75</v>
       </c>
       <c r="H14" s="10">
         <v>1.0</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I14" s="4">
         <v>50000.0</v>
       </c>
-      <c r="J14" s="5" t="s">
-        <v>11</v>
+      <c r="J14" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="12">
         <v>46100.0</v>
       </c>
-      <c r="M14" s="5">
+      <c r="M14" s="4">
         <v>70000.0</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O14" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="P14" s="5">
+        <v>3</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="4">
         <v>20000.0</v>
       </c>
       <c r="Q14" s="14">
@@ -1639,41 +1639,41 @@
       <c r="C15" s="10">
         <v>3514.0</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="G15" s="4" t="s">
         <v>77</v>
       </c>
       <c r="H15" s="10">
         <v>3.0</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15" s="4">
         <v>15000.0</v>
       </c>
-      <c r="J15" s="5" t="s">
+      <c r="J15" s="4" t="s">
         <v>35</v>
       </c>
       <c r="K15" s="11"/>
       <c r="L15" s="15">
         <v>46109.0</v>
       </c>
-      <c r="M15" s="5">
+      <c r="M15" s="4">
         <v>35000.0</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="P15" s="5">
+        <v>5</v>
+      </c>
+      <c r="O15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="P15" s="4">
         <v>20000.0</v>
       </c>
       <c r="Q15" s="14">
@@ -1690,41 +1690,41 @@
       <c r="C16" s="10">
         <v>3570.0</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="4" t="s">
         <v>79</v>
       </c>
       <c r="H16" s="10">
         <v>1.0</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I16" s="4">
         <v>10000.0</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="J16" s="4" t="s">
         <v>35</v>
       </c>
       <c r="K16" s="11"/>
       <c r="L16" s="12">
         <v>46118.0</v>
       </c>
-      <c r="M16" s="5">
+      <c r="M16" s="4">
         <v>15000.0</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="P16" s="5">
+        <v>5</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="P16" s="4">
         <v>5000.0</v>
       </c>
       <c r="Q16" s="14">
@@ -1741,41 +1741,41 @@
       <c r="C17" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="4" t="s">
         <v>82</v>
       </c>
       <c r="H17" s="10">
         <v>1.0</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17" s="4">
         <v>15000.0</v>
       </c>
-      <c r="J17" s="5" t="s">
+      <c r="J17" s="4" t="s">
         <v>35</v>
       </c>
       <c r="K17" s="11"/>
       <c r="L17" s="15">
         <v>46127.0</v>
       </c>
-      <c r="M17" s="5">
+      <c r="M17" s="4">
         <v>25000.0</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="P17" s="5">
+        <v>5</v>
+      </c>
+      <c r="O17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="P17" s="4">
         <v>10000.0</v>
       </c>
       <c r="Q17" s="14">
@@ -1792,41 +1792,41 @@
       <c r="C18" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="4" t="s">
         <v>82</v>
       </c>
       <c r="H18" s="10">
         <v>1.0</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18" s="4">
         <v>10000.0</v>
       </c>
-      <c r="J18" s="5" t="s">
+      <c r="J18" s="4" t="s">
         <v>35</v>
       </c>
       <c r="K18" s="11"/>
       <c r="L18" s="12">
         <v>46136.0</v>
       </c>
-      <c r="M18" s="5">
+      <c r="M18" s="4">
         <v>20000.0</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="P18" s="5">
+        <v>5</v>
+      </c>
+      <c r="O18" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="P18" s="4">
         <v>10000.0</v>
       </c>
       <c r="Q18" s="14">
@@ -1843,41 +1843,41 @@
       <c r="C19" s="10">
         <v>3675.0</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G19" s="4" t="s">
         <v>86</v>
       </c>
       <c r="H19" s="10">
         <v>4.0</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I19" s="4">
         <v>10000.0</v>
       </c>
-      <c r="J19" s="5" t="s">
+      <c r="J19" s="4" t="s">
         <v>35</v>
       </c>
       <c r="K19" s="11"/>
       <c r="L19" s="15">
         <v>46145.0</v>
       </c>
-      <c r="M19" s="5">
+      <c r="M19" s="4">
         <v>20000.0</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="P19" s="5">
+        <v>5</v>
+      </c>
+      <c r="O19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="P19" s="4">
         <v>10000.0</v>
       </c>
       <c r="Q19" s="14">
@@ -1892,37 +1892,37 @@
         <v>29</v>
       </c>
       <c r="C20" s="16"/>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="4" t="s">
         <v>88</v>
       </c>
       <c r="E20" s="10"/>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G20" s="17" t="s">
         <v>89</v>
       </c>
       <c r="H20" s="16"/>
-      <c r="I20" s="5">
+      <c r="I20" s="4">
         <v>28000.0</v>
       </c>
-      <c r="J20" s="5" t="s">
-        <v>16</v>
+      <c r="J20" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="K20" s="11"/>
       <c r="L20" s="12">
         <v>46154.0</v>
       </c>
-      <c r="M20" s="5">
+      <c r="M20" s="4">
         <v>30000.0</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="P20" s="5">
+        <v>5</v>
+      </c>
+      <c r="O20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="P20" s="4">
         <v>2000.0</v>
       </c>
       <c r="Q20" s="14">
@@ -1937,39 +1937,39 @@
         <v>29</v>
       </c>
       <c r="C21" s="16"/>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="4" t="s">
         <v>91</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="4" t="s">
         <v>93</v>
       </c>
       <c r="H21" s="16"/>
-      <c r="I21" s="5">
+      <c r="I21" s="4">
         <v>45000.0</v>
       </c>
-      <c r="J21" s="5" t="s">
+      <c r="J21" s="4" t="s">
         <v>39</v>
       </c>
       <c r="K21" s="11"/>
       <c r="L21" s="15">
         <v>46163.0</v>
       </c>
-      <c r="M21" s="5">
+      <c r="M21" s="4">
         <v>52000.0</v>
       </c>
       <c r="N21" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="O21" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="P21" s="5">
+        <v>7</v>
+      </c>
+      <c r="O21" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="4">
         <v>7000.0</v>
       </c>
       <c r="Q21" s="14">
@@ -1984,41 +1984,41 @@
         <v>29</v>
       </c>
       <c r="C22" s="16"/>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="4" t="s">
         <v>91</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="G22" s="4" t="s">
         <v>95</v>
       </c>
       <c r="H22" s="10">
         <v>2.0</v>
       </c>
-      <c r="I22" s="5">
+      <c r="I22" s="4">
         <v>50000.0</v>
       </c>
-      <c r="J22" s="5" t="s">
+      <c r="J22" s="4" t="s">
         <v>70</v>
       </c>
       <c r="K22" s="11"/>
       <c r="L22" s="12">
         <v>46172.0</v>
       </c>
-      <c r="M22" s="5">
+      <c r="M22" s="4">
         <v>80000.0</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="O22" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="P22" s="5">
+        <v>7</v>
+      </c>
+      <c r="O22" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="4">
         <v>30000.0</v>
       </c>
       <c r="Q22" s="14">
@@ -2035,41 +2035,41 @@
       <c r="C23" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F23" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="G23" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H23" s="10">
         <v>1.0</v>
       </c>
-      <c r="I23" s="5">
+      <c r="I23" s="4">
         <v>15000.0</v>
       </c>
-      <c r="J23" s="5" t="s">
-        <v>11</v>
+      <c r="J23" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="K23" s="11"/>
       <c r="L23" s="15">
         <v>46181.0</v>
       </c>
-      <c r="M23" s="5">
+      <c r="M23" s="4">
         <v>35000.0</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="O23" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="P23" s="5">
+        <v>7</v>
+      </c>
+      <c r="O23" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="P23" s="4">
         <v>20000.0</v>
       </c>
       <c r="Q23" s="14">
@@ -2084,39 +2084,39 @@
         <v>29</v>
       </c>
       <c r="C24" s="16"/>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="F24" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="G24" s="4" t="s">
         <v>98</v>
       </c>
       <c r="H24" s="16"/>
-      <c r="I24" s="5">
+      <c r="I24" s="4">
         <v>8000.0</v>
       </c>
-      <c r="J24" s="5" t="s">
+      <c r="J24" s="4" t="s">
         <v>70</v>
       </c>
       <c r="K24" s="11"/>
       <c r="L24" s="12">
         <v>46190.0</v>
       </c>
-      <c r="M24" s="5">
+      <c r="M24" s="4">
         <v>12000.0</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="O24" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="P24" s="5">
+        <v>9</v>
+      </c>
+      <c r="O24" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P24" s="4">
         <v>4000.0</v>
       </c>
       <c r="Q24" s="14">
@@ -2131,39 +2131,39 @@
         <v>29</v>
       </c>
       <c r="C25" s="16"/>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F25" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G25" s="5" t="s">
+      <c r="G25" s="4" t="s">
         <v>100</v>
       </c>
       <c r="H25" s="16"/>
-      <c r="I25" s="5">
+      <c r="I25" s="4">
         <v>12000.0</v>
       </c>
-      <c r="J25" s="5" t="s">
-        <v>11</v>
+      <c r="J25" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="K25" s="11"/>
       <c r="L25" s="15">
         <v>46199.0</v>
       </c>
-      <c r="M25" s="5">
+      <c r="M25" s="4">
         <v>13000.0</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="O25" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="P25" s="5">
+        <v>9</v>
+      </c>
+      <c r="O25" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P25" s="4">
         <v>1000.0</v>
       </c>
       <c r="Q25" s="14">
@@ -2180,41 +2180,41 @@
       <c r="C26" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F26" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="G26" s="4" t="s">
         <v>103</v>
       </c>
       <c r="H26" s="10">
         <v>1.0</v>
       </c>
-      <c r="I26" s="5">
+      <c r="I26" s="4">
         <v>30000.0</v>
       </c>
-      <c r="J26" s="5" t="s">
+      <c r="J26" s="4" t="s">
         <v>35</v>
       </c>
       <c r="K26" s="11"/>
       <c r="L26" s="12">
         <v>46208.0</v>
       </c>
-      <c r="M26" s="5">
+      <c r="M26" s="4">
         <v>45000.0</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="O26" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="P26" s="5">
+        <v>11</v>
+      </c>
+      <c r="O26" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P26" s="4">
         <v>15000.0</v>
       </c>
       <c r="Q26" s="14">
@@ -2231,41 +2231,41 @@
       <c r="C27" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="F27" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G27" s="5" t="s">
+      <c r="G27" s="4" t="s">
         <v>106</v>
       </c>
       <c r="H27" s="10">
         <v>2.0</v>
       </c>
-      <c r="I27" s="5">
+      <c r="I27" s="4">
         <v>40000.0</v>
       </c>
-      <c r="J27" s="5" t="s">
-        <v>11</v>
+      <c r="J27" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="K27" s="11"/>
       <c r="L27" s="15">
         <v>46217.0</v>
       </c>
-      <c r="M27" s="5">
+      <c r="M27" s="4">
         <v>75000.0</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O27" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="P27" s="5">
+        <v>11</v>
+      </c>
+      <c r="O27" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P27" s="4">
         <v>35000.0</v>
       </c>
       <c r="Q27" s="14">
@@ -2282,37 +2282,37 @@
       <c r="C28" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="4" t="s">
         <v>109</v>
       </c>
       <c r="E28" s="16"/>
-      <c r="F28" s="5" t="s">
+      <c r="F28" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="G28" s="4" t="s">
         <v>111</v>
       </c>
       <c r="H28" s="16"/>
-      <c r="I28" s="5">
+      <c r="I28" s="4">
         <v>12000.0</v>
       </c>
-      <c r="J28" s="5" t="s">
+      <c r="J28" s="4" t="s">
         <v>39</v>
       </c>
       <c r="K28" s="11"/>
       <c r="L28" s="12">
         <v>46226.0</v>
       </c>
-      <c r="M28" s="5">
+      <c r="M28" s="4">
         <v>25000.0</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="O28" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="P28" s="5">
+        <v>11</v>
+      </c>
+      <c r="O28" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P28" s="4">
         <v>13000.0</v>
       </c>
       <c r="Q28" s="14">
@@ -2329,37 +2329,37 @@
       <c r="C29" s="10">
         <v>7170.0</v>
       </c>
-      <c r="D29" s="5" t="s">
-        <v>13</v>
+      <c r="D29" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="E29" s="16"/>
-      <c r="F29" s="5" t="s">
+      <c r="F29" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="G29" s="4" t="s">
         <v>113</v>
       </c>
       <c r="H29" s="16"/>
-      <c r="I29" s="5">
+      <c r="I29" s="4">
         <v>8000.0</v>
       </c>
-      <c r="J29" s="5" t="s">
+      <c r="J29" s="4" t="s">
         <v>39</v>
       </c>
       <c r="K29" s="11"/>
       <c r="L29" s="15">
         <v>46235.0</v>
       </c>
-      <c r="M29" s="5">
+      <c r="M29" s="4">
         <v>15000.0</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O29" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="P29" s="5">
+        <v>11</v>
+      </c>
+      <c r="O29" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P29" s="4">
         <v>7000.0</v>
       </c>
       <c r="Q29" s="14">
@@ -2374,37 +2374,37 @@
         <v>29</v>
       </c>
       <c r="C30" s="16"/>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="4" t="s">
         <v>88</v>
       </c>
       <c r="E30" s="16"/>
-      <c r="F30" s="5" t="s">
+      <c r="F30" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G30" s="5" t="s">
+      <c r="G30" s="4" t="s">
         <v>115</v>
       </c>
       <c r="H30" s="16"/>
-      <c r="I30" s="5">
+      <c r="I30" s="4">
         <v>300.0</v>
       </c>
-      <c r="J30" s="5" t="s">
+      <c r="J30" s="4" t="s">
         <v>70</v>
       </c>
       <c r="K30" s="11"/>
       <c r="L30" s="12">
         <v>46244.0</v>
       </c>
-      <c r="M30" s="5">
+      <c r="M30" s="4">
         <v>10000.0</v>
       </c>
       <c r="N30" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="O30" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="P30" s="5">
+        <v>11</v>
+      </c>
+      <c r="O30" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P30" s="4">
         <v>9700.0</v>
       </c>
       <c r="Q30" s="14">
@@ -2421,41 +2421,41 @@
       <c r="C31" s="10">
         <v>3004.0</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D31" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="F31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G31" s="5" t="s">
+      <c r="G31" s="4" t="s">
         <v>118</v>
       </c>
       <c r="H31" s="10">
         <v>1.0</v>
       </c>
-      <c r="I31" s="5">
+      <c r="I31" s="4">
         <v>39000.0</v>
       </c>
-      <c r="J31" s="5" t="s">
+      <c r="J31" s="4" t="s">
         <v>44</v>
       </c>
       <c r="K31" s="11"/>
       <c r="L31" s="15">
         <v>46253.0</v>
       </c>
-      <c r="M31" s="5">
+      <c r="M31" s="4">
         <v>50000.0</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O31" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="P31" s="5">
+        <v>11</v>
+      </c>
+      <c r="O31" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P31" s="4">
         <v>11000.0</v>
       </c>
       <c r="Q31" s="14">
@@ -2472,39 +2472,39 @@
       <c r="C32" s="10">
         <v>1575.0</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="4" t="s">
         <v>88</v>
       </c>
       <c r="E32" s="16"/>
-      <c r="F32" s="5" t="s">
+      <c r="F32" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G32" s="5" t="s">
+      <c r="G32" s="4" t="s">
         <v>120</v>
       </c>
       <c r="H32" s="10">
         <v>2.0</v>
       </c>
-      <c r="I32" s="5">
+      <c r="I32" s="4">
         <v>12000.0</v>
       </c>
-      <c r="J32" s="5" t="s">
-        <v>11</v>
+      <c r="J32" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="K32" s="11"/>
       <c r="L32" s="12">
         <v>46262.0</v>
       </c>
-      <c r="M32" s="5">
+      <c r="M32" s="4">
         <v>25000.0</v>
       </c>
       <c r="N32" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="O32" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="P32" s="5">
+        <v>11</v>
+      </c>
+      <c r="O32" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P32" s="4">
         <v>13000.0</v>
       </c>
       <c r="Q32" s="14">
@@ -2521,39 +2521,39 @@
       <c r="C33" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D33" s="4" t="s">
         <v>91</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="F33" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G33" s="5" t="s">
+      <c r="G33" s="4" t="s">
         <v>124</v>
       </c>
       <c r="H33" s="16"/>
-      <c r="I33" s="5">
+      <c r="I33" s="4">
         <v>8000.0</v>
       </c>
-      <c r="J33" s="5" t="s">
+      <c r="J33" s="4" t="s">
         <v>44</v>
       </c>
       <c r="K33" s="11"/>
       <c r="L33" s="15">
         <v>46271.0</v>
       </c>
-      <c r="M33" s="5">
+      <c r="M33" s="4">
         <v>15000.0</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O33" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="P33" s="5">
+        <v>11</v>
+      </c>
+      <c r="O33" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P33" s="4">
         <v>7000.0</v>
       </c>
       <c r="Q33" s="14">
@@ -2570,39 +2570,39 @@
       <c r="C34" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D34" s="4" t="s">
         <v>91</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="F34" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G34" s="5" t="s">
+      <c r="G34" s="4" t="s">
         <v>69</v>
       </c>
       <c r="H34" s="16"/>
-      <c r="I34" s="5">
+      <c r="I34" s="4">
         <v>12000.0</v>
       </c>
-      <c r="J34" s="5" t="s">
+      <c r="J34" s="4" t="s">
         <v>44</v>
       </c>
       <c r="K34" s="11"/>
       <c r="L34" s="12">
         <v>46280.0</v>
       </c>
-      <c r="M34" s="5">
+      <c r="M34" s="4">
         <v>20000.0</v>
       </c>
       <c r="N34" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="O34" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="P34" s="5">
+        <v>11</v>
+      </c>
+      <c r="O34" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P34" s="4">
         <v>8000.0</v>
       </c>
       <c r="Q34" s="14">
@@ -2619,41 +2619,41 @@
       <c r="C35" s="10">
         <v>7071.0</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="4" t="s">
         <v>91</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="F35" s="5" t="s">
+      <c r="F35" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G35" s="5" t="s">
+      <c r="G35" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H35" s="10">
         <v>1.0</v>
       </c>
-      <c r="I35" s="5">
+      <c r="I35" s="4">
         <v>12000.0</v>
       </c>
-      <c r="J35" s="5" t="s">
+      <c r="J35" s="4" t="s">
         <v>39</v>
       </c>
       <c r="K35" s="11"/>
       <c r="L35" s="15">
         <v>46281.0</v>
       </c>
-      <c r="M35" s="5">
+      <c r="M35" s="4">
         <v>22000.0</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O35" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="P35" s="5">
+        <v>11</v>
+      </c>
+      <c r="O35" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P35" s="4">
         <v>10000.0</v>
       </c>
       <c r="Q35" s="14">
@@ -2670,41 +2670,41 @@
       <c r="C36" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" s="4" t="s">
         <v>91</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="F36" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G36" s="5" t="s">
+      <c r="G36" s="4" t="s">
         <v>132</v>
       </c>
       <c r="H36" s="10">
         <v>4.0</v>
       </c>
-      <c r="I36" s="5">
+      <c r="I36" s="4">
         <v>20000.0</v>
       </c>
-      <c r="J36" s="5" t="s">
+      <c r="J36" s="4" t="s">
         <v>44</v>
       </c>
       <c r="K36" s="11"/>
       <c r="L36" s="12">
         <v>46282.0</v>
       </c>
-      <c r="M36" s="5">
+      <c r="M36" s="4">
         <v>30000.0</v>
       </c>
       <c r="N36" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="O36" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="P36" s="5">
+        <v>11</v>
+      </c>
+      <c r="O36" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P36" s="4">
         <v>10000.0</v>
       </c>
       <c r="Q36" s="14">
@@ -2721,41 +2721,41 @@
       <c r="C37" s="10">
         <v>7005.0</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D37" s="4" t="s">
         <v>91</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="F37" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G37" s="5" t="s">
+      <c r="G37" s="4" t="s">
         <v>134</v>
       </c>
       <c r="H37" s="10">
         <v>4.0</v>
       </c>
-      <c r="I37" s="5">
+      <c r="I37" s="4">
         <v>20000.0</v>
       </c>
-      <c r="J37" s="5" t="s">
+      <c r="J37" s="4" t="s">
         <v>44</v>
       </c>
       <c r="K37" s="11"/>
       <c r="L37" s="15">
         <v>46283.0</v>
       </c>
-      <c r="M37" s="5">
+      <c r="M37" s="4">
         <v>35000.0</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O37" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="P37" s="5">
+        <v>11</v>
+      </c>
+      <c r="O37" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P37" s="4">
         <v>15000.0</v>
       </c>
       <c r="Q37" s="14">
@@ -2772,41 +2772,41 @@
       <c r="C38" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D38" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="F38" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G38" s="5" t="s">
+      <c r="G38" s="4" t="s">
         <v>136</v>
       </c>
       <c r="H38" s="10">
         <v>1.0</v>
       </c>
-      <c r="I38" s="5">
+      <c r="I38" s="4">
         <v>20000.0</v>
       </c>
-      <c r="J38" s="5" t="s">
-        <v>11</v>
+      <c r="J38" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="K38" s="11"/>
       <c r="L38" s="12">
         <v>46284.0</v>
       </c>
-      <c r="M38" s="5">
+      <c r="M38" s="4">
         <v>70000.0</v>
       </c>
       <c r="N38" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="O38" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="P38" s="5">
+        <v>11</v>
+      </c>
+      <c r="O38" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P38" s="4">
         <v>50000.0</v>
       </c>
       <c r="Q38" s="14">
@@ -2821,39 +2821,39 @@
         <v>29</v>
       </c>
       <c r="C39" s="16"/>
-      <c r="D39" s="5" t="s">
+      <c r="D39" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="F39" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G39" s="5" t="s">
+      <c r="G39" s="4" t="s">
         <v>138</v>
       </c>
       <c r="H39" s="16"/>
-      <c r="I39" s="5">
+      <c r="I39" s="4">
         <v>35000.0</v>
       </c>
-      <c r="J39" s="5" t="s">
+      <c r="J39" s="4" t="s">
         <v>70</v>
       </c>
       <c r="K39" s="11"/>
       <c r="L39" s="15">
         <v>46285.0</v>
       </c>
-      <c r="M39" s="5">
+      <c r="M39" s="4">
         <v>60000.0</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O39" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="P39" s="5">
+        <v>11</v>
+      </c>
+      <c r="O39" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P39" s="4">
         <v>25000.0</v>
       </c>
       <c r="Q39" s="14">
@@ -2868,39 +2868,39 @@
         <v>29</v>
       </c>
       <c r="C40" s="16"/>
-      <c r="D40" s="5" t="s">
+      <c r="D40" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="F40" s="5" t="s">
+      <c r="F40" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G40" s="5" t="s">
+      <c r="G40" s="4" t="s">
         <v>140</v>
       </c>
       <c r="H40" s="16"/>
-      <c r="I40" s="5">
+      <c r="I40" s="4">
         <v>70000.0</v>
       </c>
-      <c r="J40" s="5" t="s">
+      <c r="J40" s="4" t="s">
         <v>39</v>
       </c>
       <c r="K40" s="11"/>
       <c r="L40" s="12">
         <v>46286.0</v>
       </c>
-      <c r="M40" s="5">
+      <c r="M40" s="4">
         <v>100000.0</v>
       </c>
       <c r="N40" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="O40" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="P40" s="5">
+        <v>11</v>
+      </c>
+      <c r="O40" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P40" s="4">
         <v>30000.0</v>
       </c>
       <c r="Q40" s="14">
@@ -2915,39 +2915,39 @@
         <v>29</v>
       </c>
       <c r="C41" s="16"/>
-      <c r="D41" s="5" t="s">
+      <c r="D41" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F41" s="5" t="s">
+      <c r="F41" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G41" s="5" t="s">
+      <c r="G41" s="4" t="s">
         <v>98</v>
       </c>
       <c r="H41" s="16"/>
-      <c r="I41" s="5">
+      <c r="I41" s="4">
         <v>34000.0</v>
       </c>
-      <c r="J41" s="5" t="s">
+      <c r="J41" s="4" t="s">
         <v>70</v>
       </c>
       <c r="K41" s="11"/>
       <c r="L41" s="15">
         <v>46287.0</v>
       </c>
-      <c r="M41" s="5">
+      <c r="M41" s="4">
         <v>40000.0</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O41" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="P41" s="5">
+        <v>11</v>
+      </c>
+      <c r="O41" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P41" s="4">
         <v>6000.0</v>
       </c>
       <c r="Q41" s="14">
@@ -2962,39 +2962,39 @@
         <v>29</v>
       </c>
       <c r="C42" s="16"/>
-      <c r="D42" s="5" t="s">
+      <c r="D42" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="F42" s="4" t="s">
         <v>61</v>
       </c>
       <c r="G42" s="13" t="s">
         <v>143</v>
       </c>
       <c r="H42" s="16"/>
-      <c r="I42" s="5">
+      <c r="I42" s="4">
         <v>15000.0</v>
       </c>
-      <c r="J42" s="5" t="s">
-        <v>11</v>
+      <c r="J42" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="K42" s="11"/>
       <c r="L42" s="12">
         <v>46288.0</v>
       </c>
-      <c r="M42" s="5">
+      <c r="M42" s="4">
         <v>40000.0</v>
       </c>
       <c r="N42" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="O42" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="P42" s="5">
+        <v>11</v>
+      </c>
+      <c r="O42" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P42" s="4">
         <v>25000.0</v>
       </c>
       <c r="Q42" s="14">
@@ -3011,41 +3011,41 @@
       <c r="C43" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="D43" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="F43" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G43" s="5" t="s">
+      <c r="G43" s="4" t="s">
         <v>146</v>
       </c>
       <c r="H43" s="10">
         <v>1.0</v>
       </c>
-      <c r="I43" s="5">
+      <c r="I43" s="4">
         <v>15000.0</v>
       </c>
-      <c r="J43" s="5" t="s">
-        <v>11</v>
+      <c r="J43" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="K43" s="11"/>
       <c r="L43" s="15">
         <v>46289.0</v>
       </c>
-      <c r="M43" s="5">
+      <c r="M43" s="4">
         <v>30000.0</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O43" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="P43" s="5">
+        <v>11</v>
+      </c>
+      <c r="O43" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P43" s="4">
         <v>15000.0</v>
       </c>
       <c r="Q43" s="14">
@@ -3060,39 +3060,39 @@
         <v>29</v>
       </c>
       <c r="C44" s="16"/>
-      <c r="D44" s="5" t="s">
+      <c r="D44" s="4" t="s">
         <v>109</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="F44" s="5" t="s">
+      <c r="F44" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G44" s="5" t="s">
+      <c r="G44" s="4" t="s">
         <v>148</v>
       </c>
       <c r="H44" s="16"/>
-      <c r="I44" s="5">
+      <c r="I44" s="4">
         <v>28000.0</v>
       </c>
-      <c r="J44" s="5" t="s">
+      <c r="J44" s="4" t="s">
         <v>44</v>
       </c>
       <c r="K44" s="11"/>
       <c r="L44" s="12">
         <v>46290.0</v>
       </c>
-      <c r="M44" s="5">
+      <c r="M44" s="4">
         <v>35000.0</v>
       </c>
       <c r="N44" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="O44" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="P44" s="5">
+        <v>11</v>
+      </c>
+      <c r="O44" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P44" s="4">
         <v>7000.0</v>
       </c>
       <c r="Q44" s="14">
@@ -3107,39 +3107,39 @@
         <v>29</v>
       </c>
       <c r="C45" s="16"/>
-      <c r="D45" s="5" t="s">
+      <c r="D45" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F45" s="5" t="s">
+      <c r="F45" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G45" s="5" t="s">
+      <c r="G45" s="4" t="s">
         <v>150</v>
       </c>
       <c r="H45" s="16"/>
-      <c r="I45" s="5">
+      <c r="I45" s="4">
         <v>42000.0</v>
       </c>
-      <c r="J45" s="5" t="s">
+      <c r="J45" s="4" t="s">
         <v>151</v>
       </c>
       <c r="K45" s="11"/>
       <c r="L45" s="15">
         <v>46291.0</v>
       </c>
-      <c r="M45" s="5">
+      <c r="M45" s="4">
         <v>50000.0</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O45" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="P45" s="5">
+        <v>11</v>
+      </c>
+      <c r="O45" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P45" s="4">
         <v>8000.0</v>
       </c>
       <c r="Q45" s="14">
@@ -3154,41 +3154,41 @@
         <v>29</v>
       </c>
       <c r="C46" s="16"/>
-      <c r="D46" s="5" t="s">
+      <c r="D46" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E46" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F46" s="5" t="s">
+      <c r="F46" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G46" s="5" t="s">
+      <c r="G46" s="4" t="s">
         <v>153</v>
       </c>
       <c r="H46" s="10">
         <v>1.0</v>
       </c>
-      <c r="I46" s="5">
+      <c r="I46" s="4">
         <v>45000.0</v>
       </c>
-      <c r="J46" s="5" t="s">
+      <c r="J46" s="4" t="s">
         <v>154</v>
       </c>
       <c r="K46" s="11"/>
       <c r="L46" s="12">
         <v>46292.0</v>
       </c>
-      <c r="M46" s="5">
+      <c r="M46" s="4">
         <v>65000.0</v>
       </c>
       <c r="N46" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="O46" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="P46" s="5">
+        <v>11</v>
+      </c>
+      <c r="O46" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P46" s="4">
         <v>20000.0</v>
       </c>
       <c r="Q46" s="14">
@@ -3203,39 +3203,39 @@
         <v>29</v>
       </c>
       <c r="C47" s="16"/>
-      <c r="D47" s="5" t="s">
+      <c r="D47" s="4" t="s">
         <v>91</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="F47" s="5" t="s">
+      <c r="F47" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G47" s="5" t="s">
+      <c r="G47" s="4" t="s">
         <v>156</v>
       </c>
       <c r="H47" s="16"/>
-      <c r="I47" s="5">
+      <c r="I47" s="4">
         <v>28000.0</v>
       </c>
-      <c r="J47" s="5" t="s">
+      <c r="J47" s="4" t="s">
         <v>39</v>
       </c>
       <c r="K47" s="11"/>
       <c r="L47" s="15">
         <v>46293.0</v>
       </c>
-      <c r="M47" s="5">
+      <c r="M47" s="4">
         <v>36000.0</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O47" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="P47" s="5">
+        <v>11</v>
+      </c>
+      <c r="O47" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P47" s="4">
         <v>8000.0</v>
       </c>
       <c r="Q47" s="14">
@@ -3250,39 +3250,39 @@
         <v>29</v>
       </c>
       <c r="C48" s="16"/>
-      <c r="D48" s="5" t="s">
+      <c r="D48" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="F48" s="5" t="s">
+      <c r="F48" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G48" s="5" t="s">
+      <c r="G48" s="4" t="s">
         <v>158</v>
       </c>
       <c r="H48" s="16"/>
-      <c r="I48" s="5">
+      <c r="I48" s="4">
         <v>6000.0</v>
       </c>
-      <c r="J48" s="5" t="s">
+      <c r="J48" s="4" t="s">
         <v>70</v>
       </c>
       <c r="K48" s="11"/>
       <c r="L48" s="12">
         <v>46294.0</v>
       </c>
-      <c r="M48" s="5">
+      <c r="M48" s="4">
         <v>25000.0</v>
       </c>
       <c r="N48" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="O48" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="P48" s="5">
+        <v>11</v>
+      </c>
+      <c r="O48" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P48" s="4">
         <v>19000.0</v>
       </c>
       <c r="Q48" s="14">
@@ -3328,7 +3328,7 @@
       <c r="C50" s="9">
         <v>3004.0</v>
       </c>
-      <c r="D50" s="5" t="s">
+      <c r="D50" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E50" s="10" t="s">
@@ -3357,7 +3357,7 @@
       <c r="C51" s="9">
         <v>1575.0</v>
       </c>
-      <c r="D51" s="5" t="s">
+      <c r="D51" s="4" t="s">
         <v>88</v>
       </c>
       <c r="E51" s="16"/>
@@ -3552,7 +3552,7 @@
       <c r="C58" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D58" s="5" t="s">
+      <c r="D58" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E58" s="10" t="s">
@@ -9347,42 +9347,42 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>11</v>
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>13</v>
+        <v>7</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>19</v>
+        <v>11</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
